--- a/src/main/java/com/mycompany/ocxrst/BASES/REGISTROC.xlsx
+++ b/src/main/java/com/mycompany/ocxrst/BASES/REGISTROC.xlsx
@@ -1,42 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <workbookPr/>
   <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OCXRST\OrdendeComprasRST\src\main\java\com\mycompany\ocxrst\BASES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42AD64EC-0395-47B7-B9D1-BAEF62365138}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A971BD09-E430-4C27-A9A6-26F4A98F85A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{1A5C3FBD-CC1E-4D2B-B7AC-82264016413D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{1A5C3FBD-CC1E-4D2B-B7AC-82264016413D}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="98">
   <si>
     <t>FECHA</t>
   </si>
@@ -158,9 +150,6 @@
     <t>$ 4,534.59</t>
   </si>
   <si>
-    <t>PROYECTA</t>
-  </si>
-  <si>
     <t>25</t>
   </si>
   <si>
@@ -194,9 +183,6 @@
     <t>LACT01</t>
   </si>
   <si>
-    <t>PRUEBA DOS</t>
-  </si>
-  <si>
     <t>Crédito</t>
   </si>
   <si>
@@ -206,21 +192,9 @@
     <t>PPD (pago por partes)</t>
   </si>
   <si>
-    <t>$ 6,046.64</t>
-  </si>
-  <si>
-    <t>$ 967.46</t>
-  </si>
-  <si>
-    <t>$ 7,014.10</t>
-  </si>
-  <si>
     <t>jume06</t>
   </si>
   <si>
-    <t>GRANDE</t>
-  </si>
-  <si>
     <t>$ 20,795.79</t>
   </si>
   <si>
@@ -315,6 +289,39 @@
   </si>
   <si>
     <t>$ 4,559.17</t>
+  </si>
+  <si>
+    <t>MONTOPAGADO</t>
+  </si>
+  <si>
+    <t>DIASTRASCURRIDOS</t>
+  </si>
+  <si>
+    <t>STATUS</t>
+  </si>
+  <si>
+    <t>$ 3,000.00</t>
+  </si>
+  <si>
+    <t>AVANTE20260904</t>
+  </si>
+  <si>
+    <t>herd05</t>
+  </si>
+  <si>
+    <t>ASDASD</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>$ 5,378.26</t>
+  </si>
+  <si>
+    <t>$ 860.52</t>
+  </si>
+  <si>
+    <t>$ 6,238.78</t>
   </si>
 </sst>
 </file>
@@ -324,7 +331,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd/MM/yyyy"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -359,19 +366,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
   </cellXfs>
   <cellStyles count="1">
@@ -707,29 +711,31 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45D375DD-15B7-4F53-9122-30FA48C9EA3E}">
-  <dimension ref="A1:V9"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:Y10"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="9.54296875" collapsed="true"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="9.5" collapsed="true"/>
     <col min="2" max="2" bestFit="true" customWidth="true" width="13.0" collapsed="true"/>
     <col min="3" max="3" bestFit="true" customWidth="true" width="12.0" collapsed="true"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="11.1796875" collapsed="true"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="13.7265625" collapsed="true"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="11.125" collapsed="true"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="13.75" collapsed="true"/>
     <col min="6" max="7" bestFit="true" customWidth="true" width="11.0" collapsed="true"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" width="9.90625" collapsed="true"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" width="9.875" collapsed="true"/>
     <col min="9" max="9" bestFit="true" customWidth="true" width="11.0" collapsed="true"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" width="11.6328125" collapsed="true"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" width="11.625" collapsed="true"/>
     <col min="11" max="11" bestFit="true" customWidth="true" width="13.0" collapsed="true"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" width="13.7265625" collapsed="true"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" width="13.1796875" collapsed="true"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" width="20.1796875" collapsed="true"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" width="13.75" collapsed="true"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" width="13.125" collapsed="true"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" width="20.125" collapsed="true"/>
     <col min="15" max="15" bestFit="true" customWidth="true" width="12.0" collapsed="true"/>
     <col min="16" max="16" bestFit="true" customWidth="true" width="11.0" collapsed="true"/>
-    <col min="17" max="17" customWidth="true" width="13.54296875" collapsed="true"/>
-    <col min="18" max="18" customWidth="true" width="13.7265625" collapsed="true"/>
+    <col min="17" max="17" customWidth="true" width="13.5" collapsed="true"/>
+    <col min="18" max="18" customWidth="true" width="13.75" collapsed="true"/>
+    <col min="23" max="23" customWidth="true" width="15.75" collapsed="true"/>
+    <col min="24" max="24" bestFit="true" customWidth="true" width="19.875" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:25">
       <c r="A1" t="s">
         <v>18</v>
       </c>
@@ -796,8 +802,17 @@
       <c r="V1" t="s">
         <v>19</v>
       </c>
+      <c r="W1" t="s">
+        <v>87</v>
+      </c>
+      <c r="X1" t="s">
+        <v>88</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>89</v>
+      </c>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -864,13 +879,16 @@
       <c r="V2" t="s">
         <v>39</v>
       </c>
+      <c r="W2" t="s">
+        <v>39</v>
+      </c>
     </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="B3" t="n" s="12">
-        <v>46127.0</v>
+    <row r="3" spans="1:25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" s="8">
+        <v>46127</v>
       </c>
       <c r="C3" t="s">
         <v>21</v>
@@ -888,7 +906,7 @@
         <v>25</v>
       </c>
       <c r="H3" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="I3" t="s">
         <v>27</v>
@@ -900,13 +918,13 @@
         <v>29</v>
       </c>
       <c r="L3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="M3" t="s">
         <v>31</v>
       </c>
       <c r="N3" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="O3" t="s">
         <v>33</v>
@@ -915,7 +933,7 @@
         <v>25</v>
       </c>
       <c r="Q3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R3" t="s">
         <v>35</v>
@@ -924,21 +942,24 @@
         <v>36</v>
       </c>
       <c r="T3" t="s">
+        <v>84</v>
+      </c>
+      <c r="U3" t="s">
+        <v>85</v>
+      </c>
+      <c r="V3" t="s">
+        <v>86</v>
+      </c>
+      <c r="W3" t="s">
         <v>90</v>
       </c>
-      <c r="U3" t="s">
-        <v>91</v>
-      </c>
-      <c r="V3" t="s">
-        <v>92</v>
-      </c>
     </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="B4" t="n" s="3">
-        <v>46127.0</v>
+    <row r="4" spans="1:25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2">
+        <v>46127</v>
       </c>
       <c r="C4" t="s">
         <v>21</v>
@@ -956,19 +977,19 @@
         <v>25</v>
       </c>
       <c r="H4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I4" t="s">
         <v>27</v>
       </c>
       <c r="J4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K4" t="s">
         <v>29</v>
       </c>
       <c r="L4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="M4" t="s">
         <v>31</v>
@@ -983,7 +1004,7 @@
         <v>25</v>
       </c>
       <c r="Q4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="R4" t="s">
         <v>35</v>
@@ -992,30 +1013,30 @@
         <v>36</v>
       </c>
       <c r="T4" t="s">
+        <v>42</v>
+      </c>
+      <c r="U4" t="s">
         <v>43</v>
       </c>
-      <c r="U4" t="s">
+      <c r="V4" t="s">
         <v>44</v>
       </c>
-      <c r="V4" t="s">
-        <v>45</v>
-      </c>
     </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>4.0</v>
-      </c>
-      <c r="B5" t="n" s="11">
-        <v>46128.0</v>
+    <row r="5" spans="1:25">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" s="7">
+        <v>46128</v>
       </c>
       <c r="C5" t="s">
         <v>21</v>
       </c>
       <c r="D5" t="s">
+        <v>49</v>
+      </c>
+      <c r="E5" t="s">
         <v>50</v>
-      </c>
-      <c r="E5" t="s">
-        <v>51</v>
       </c>
       <c r="F5" t="s">
         <v>24</v>
@@ -1024,19 +1045,19 @@
         <v>25</v>
       </c>
       <c r="H5" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="I5" t="s">
+        <v>51</v>
+      </c>
+      <c r="J5" t="s">
+        <v>52</v>
+      </c>
+      <c r="K5" t="s">
         <v>53</v>
       </c>
-      <c r="J5" t="s">
-        <v>54</v>
-      </c>
-      <c r="K5" t="s">
-        <v>55</v>
-      </c>
       <c r="L5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="M5" t="s">
         <v>31</v>
@@ -1051,39 +1072,39 @@
         <v>25</v>
       </c>
       <c r="Q5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R5" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="S5" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="T5" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="U5" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="V5" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="B6" t="n" s="9">
-        <v>46128.0</v>
+    <row r="6" spans="1:25">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" s="6">
+        <v>46128</v>
       </c>
       <c r="C6" t="s">
         <v>21</v>
       </c>
       <c r="D6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E6" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="F6" t="s">
         <v>24</v>
@@ -1092,22 +1113,22 @@
         <v>25</v>
       </c>
       <c r="H6" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="I6" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="J6" t="s">
         <v>28</v>
       </c>
       <c r="K6" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="L6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="M6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N6" t="s">
         <v>32</v>
@@ -1119,7 +1140,7 @@
         <v>25</v>
       </c>
       <c r="Q6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R6" t="s">
         <v>35</v>
@@ -1128,30 +1149,30 @@
         <v>36</v>
       </c>
       <c r="T6" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="U6" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="V6" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>6.0</v>
-      </c>
-      <c r="B7" t="n" s="6">
-        <v>46128.54262923611</v>
+    <row r="7" spans="1:25">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3">
+        <v>46128.542629236108</v>
       </c>
       <c r="C7" t="s">
         <v>21</v>
       </c>
       <c r="D7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E7" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="F7" t="s">
         <v>24</v>
@@ -1160,22 +1181,22 @@
         <v>25</v>
       </c>
       <c r="H7" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="I7" t="s">
+        <v>51</v>
+      </c>
+      <c r="J7" t="s">
+        <v>46</v>
+      </c>
+      <c r="K7" t="s">
         <v>53</v>
       </c>
-      <c r="J7" t="s">
+      <c r="L7" t="s">
         <v>47</v>
       </c>
-      <c r="K7" t="s">
-        <v>55</v>
-      </c>
-      <c r="L7" t="s">
-        <v>48</v>
-      </c>
       <c r="M7" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="N7" t="s">
         <v>32</v>
@@ -1187,7 +1208,7 @@
         <v>25</v>
       </c>
       <c r="Q7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R7" t="s">
         <v>35</v>
@@ -1196,30 +1217,30 @@
         <v>36</v>
       </c>
       <c r="T7" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="U7" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="V7" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>7.0</v>
-      </c>
-      <c r="B8" t="n" s="7">
+    <row r="8" spans="1:25">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" s="4">
         <v>46128.551586458336</v>
       </c>
       <c r="C8" t="s">
         <v>21</v>
       </c>
       <c r="D8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E8" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="F8" t="s">
         <v>24</v>
@@ -1228,7 +1249,7 @@
         <v>25</v>
       </c>
       <c r="H8" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="I8" t="s">
         <v>27</v>
@@ -1240,10 +1261,10 @@
         <v>29</v>
       </c>
       <c r="L8" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="M8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N8" t="s">
         <v>32</v>
@@ -1255,7 +1276,7 @@
         <v>25</v>
       </c>
       <c r="Q8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R8" t="s">
         <v>35</v>
@@ -1264,30 +1285,30 @@
         <v>36</v>
       </c>
       <c r="T8" t="s">
+        <v>42</v>
+      </c>
+      <c r="U8" t="s">
         <v>43</v>
       </c>
-      <c r="U8" t="s">
+      <c r="V8" t="s">
         <v>44</v>
       </c>
-      <c r="V8" t="s">
-        <v>45</v>
-      </c>
     </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>8.0</v>
-      </c>
-      <c r="B9" t="n" s="8">
-        <v>46129.47698445602</v>
+    <row r="9" spans="1:25">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" s="5">
+        <v>46129.476984456021</v>
       </c>
       <c r="C9" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="D9" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="E9" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="F9" t="s">
         <v>24</v>
@@ -1296,7 +1317,7 @@
         <v>25</v>
       </c>
       <c r="H9" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="I9" t="s">
         <v>27</v>
@@ -1308,10 +1329,10 @@
         <v>29</v>
       </c>
       <c r="L9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="M9" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="N9" t="s">
         <v>32</v>
@@ -1323,7 +1344,7 @@
         <v>25</v>
       </c>
       <c r="Q9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R9" t="s">
         <v>35</v>
@@ -1332,13 +1353,84 @@
         <v>36</v>
       </c>
       <c r="T9" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="U9" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="V9" t="s">
-        <v>80</v>
+        <v>74</v>
+      </c>
+      <c r="W9" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9.0</v>
+      </c>
+      <c r="B10" t="n" s="9">
+        <v>46269.711945787036</v>
+      </c>
+      <c r="C10" t="s">
+        <v>21</v>
+      </c>
+      <c r="D10" t="s">
+        <v>91</v>
+      </c>
+      <c r="E10" t="s">
+        <v>92</v>
+      </c>
+      <c r="F10" t="s">
+        <v>24</v>
+      </c>
+      <c r="G10" t="s">
+        <v>25</v>
+      </c>
+      <c r="H10" t="s">
+        <v>93</v>
+      </c>
+      <c r="I10" t="s">
+        <v>51</v>
+      </c>
+      <c r="J10" t="s">
+        <v>28</v>
+      </c>
+      <c r="K10" t="s">
+        <v>53</v>
+      </c>
+      <c r="L10" t="s">
+        <v>94</v>
+      </c>
+      <c r="M10" t="s">
+        <v>31</v>
+      </c>
+      <c r="N10" t="s">
+        <v>32</v>
+      </c>
+      <c r="O10" t="s">
+        <v>33</v>
+      </c>
+      <c r="P10" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>41</v>
+      </c>
+      <c r="R10" t="s">
+        <v>35</v>
+      </c>
+      <c r="S10" t="s">
+        <v>36</v>
+      </c>
+      <c r="T10" t="s">
+        <v>95</v>
+      </c>
+      <c r="U10" t="s">
+        <v>96</v>
+      </c>
+      <c r="V10" t="s">
+        <v>97</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/java/com/mycompany/ocxrst/BASES/REGISTROC.xlsx
+++ b/src/main/java/com/mycompany/ocxrst/BASES/REGISTROC.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="103">
   <si>
     <t>FECHA</t>
   </si>
@@ -322,6 +322,21 @@
   </si>
   <si>
     <t>$ 6,238.78</t>
+  </si>
+  <si>
+    <t>AVANTE20260907</t>
+  </si>
+  <si>
+    <t>NO</t>
+  </si>
+  <si>
+    <t>16.05</t>
+  </si>
+  <si>
+    <t>USD $ 2,272.57</t>
+  </si>
+  <si>
+    <t>USD $ 0.00</t>
   </si>
 </sst>
 </file>
@@ -366,7 +381,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -376,6 +391,7 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
   </cellXfs>
   <cellStyles count="1">
@@ -711,7 +727,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45D375DD-15B7-4F53-9122-30FA48C9EA3E}">
-  <dimension ref="A1:Y10"/>
+  <dimension ref="A1:Y11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" bestFit="true" customWidth="true" width="9.5" collapsed="true"/>
@@ -1433,6 +1449,74 @@
         <v>97</v>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="B11" t="n" s="10">
+        <v>46272.43931767361</v>
+      </c>
+      <c r="C11" t="s">
+        <v>21</v>
+      </c>
+      <c r="D11" t="s">
+        <v>98</v>
+      </c>
+      <c r="E11" t="s">
+        <v>69</v>
+      </c>
+      <c r="F11" t="s">
+        <v>24</v>
+      </c>
+      <c r="G11" t="s">
+        <v>41</v>
+      </c>
+      <c r="H11" t="s">
+        <v>26</v>
+      </c>
+      <c r="I11" t="s">
+        <v>27</v>
+      </c>
+      <c r="J11" t="s">
+        <v>28</v>
+      </c>
+      <c r="K11" t="s">
+        <v>29</v>
+      </c>
+      <c r="L11" t="s">
+        <v>66</v>
+      </c>
+      <c r="M11" t="s">
+        <v>47</v>
+      </c>
+      <c r="N11" t="s">
+        <v>71</v>
+      </c>
+      <c r="O11" t="s">
+        <v>99</v>
+      </c>
+      <c r="P11" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>41</v>
+      </c>
+      <c r="R11" t="s">
+        <v>77</v>
+      </c>
+      <c r="S11" t="s">
+        <v>100</v>
+      </c>
+      <c r="T11" t="s">
+        <v>101</v>
+      </c>
+      <c r="U11" t="s">
+        <v>102</v>
+      </c>
+      <c r="V11" t="s">
+        <v>101</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/src/main/java/com/mycompany/ocxrst/BASES/REGISTROC.xlsx
+++ b/src/main/java/com/mycompany/ocxrst/BASES/REGISTROC.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="120">
   <si>
     <t>FECHA</t>
   </si>
@@ -337,6 +337,57 @@
   </si>
   <si>
     <t>USD $ 0.00</t>
+  </si>
+  <si>
+    <t>$ 17,676.42</t>
+  </si>
+  <si>
+    <t>$ 2,828.23</t>
+  </si>
+  <si>
+    <t>$ 20,504.65</t>
+  </si>
+  <si>
+    <t>$ 5,923.30</t>
+  </si>
+  <si>
+    <t>$ 947.73</t>
+  </si>
+  <si>
+    <t>$ 6,871.03</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>AVANTE20260908</t>
+  </si>
+  <si>
+    <t>XXXXXXX</t>
+  </si>
+  <si>
+    <t>Efectivo</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>CAD</t>
+  </si>
+  <si>
+    <t>12.21</t>
+  </si>
+  <si>
+    <t>$ 1,136.44</t>
+  </si>
+  <si>
+    <t>$ 181.83</t>
+  </si>
+  <si>
+    <t>$ 1,318.28</t>
   </si>
 </sst>
 </file>
@@ -381,7 +432,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -391,6 +442,11 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
   </cellXfs>
@@ -727,7 +783,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45D375DD-15B7-4F53-9122-30FA48C9EA3E}">
-  <dimension ref="A1:Y11"/>
+  <dimension ref="A1:Y13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" bestFit="true" customWidth="true" width="9.5" collapsed="true"/>
@@ -1178,8 +1234,8 @@
       <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" s="3">
-        <v>46128.542629236108</v>
+      <c r="B7" s="13" t="n">
+        <v>46128.54262923611</v>
       </c>
       <c r="C7" t="s">
         <v>21</v>
@@ -1209,10 +1265,10 @@
         <v>53</v>
       </c>
       <c r="L7" t="s">
+        <v>109</v>
+      </c>
+      <c r="M7" t="s">
         <v>47</v>
-      </c>
-      <c r="M7" t="s">
-        <v>60</v>
       </c>
       <c r="N7" t="s">
         <v>32</v>
@@ -1515,6 +1571,142 @@
       </c>
       <c r="V11" t="s">
         <v>101</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11.0</v>
+      </c>
+      <c r="B12" t="n" s="14">
+        <v>46128.0</v>
+      </c>
+      <c r="C12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D12" t="s">
+        <v>49</v>
+      </c>
+      <c r="E12" t="s">
+        <v>54</v>
+      </c>
+      <c r="F12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G12" t="s">
+        <v>25</v>
+      </c>
+      <c r="H12" t="s">
+        <v>75</v>
+      </c>
+      <c r="I12" t="s">
+        <v>51</v>
+      </c>
+      <c r="J12" t="s">
+        <v>28</v>
+      </c>
+      <c r="K12" t="s">
+        <v>53</v>
+      </c>
+      <c r="L12" t="s">
+        <v>47</v>
+      </c>
+      <c r="M12" t="s">
+        <v>110</v>
+      </c>
+      <c r="N12" t="s">
+        <v>94</v>
+      </c>
+      <c r="O12" t="s">
+        <v>33</v>
+      </c>
+      <c r="P12" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>41</v>
+      </c>
+      <c r="R12" t="s">
+        <v>35</v>
+      </c>
+      <c r="S12" t="s">
+        <v>36</v>
+      </c>
+      <c r="T12" t="s">
+        <v>106</v>
+      </c>
+      <c r="U12" t="s">
+        <v>107</v>
+      </c>
+      <c r="V12" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12.0</v>
+      </c>
+      <c r="B13" t="n" s="15">
+        <v>46273.6649734838</v>
+      </c>
+      <c r="C13" t="s">
+        <v>21</v>
+      </c>
+      <c r="D13" t="s">
+        <v>111</v>
+      </c>
+      <c r="E13" t="s">
+        <v>58</v>
+      </c>
+      <c r="F13" t="s">
+        <v>24</v>
+      </c>
+      <c r="G13" t="s">
+        <v>41</v>
+      </c>
+      <c r="H13" t="s">
+        <v>112</v>
+      </c>
+      <c r="I13" t="s">
+        <v>27</v>
+      </c>
+      <c r="J13" t="s">
+        <v>113</v>
+      </c>
+      <c r="K13" t="s">
+        <v>53</v>
+      </c>
+      <c r="L13" t="s">
+        <v>66</v>
+      </c>
+      <c r="M13" t="s">
+        <v>114</v>
+      </c>
+      <c r="N13" t="s">
+        <v>32</v>
+      </c>
+      <c r="O13" t="s">
+        <v>33</v>
+      </c>
+      <c r="P13" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>41</v>
+      </c>
+      <c r="R13" t="s">
+        <v>115</v>
+      </c>
+      <c r="S13" t="s">
+        <v>116</v>
+      </c>
+      <c r="T13" t="s">
+        <v>117</v>
+      </c>
+      <c r="U13" t="s">
+        <v>118</v>
+      </c>
+      <c r="V13" t="s">
+        <v>119</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/java/com/mycompany/ocxrst/BASES/REGISTROC.xlsx
+++ b/src/main/java/com/mycompany/ocxrst/BASES/REGISTROC.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
   <workbookPr/>
   <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OCXRST\OrdendeComprasRST\src\main\java\com\mycompany\ocxrst\BASES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A971BD09-E430-4C27-A9A6-26F4A98F85A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2436DEE5-DABF-4AB6-BBE6-42B438C4EE72}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{1A5C3FBD-CC1E-4D2B-B7AC-82264016413D}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{1A5C3FBD-CC1E-4D2B-B7AC-82264016413D}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="110">
   <si>
     <t>FECHA</t>
   </si>
@@ -69,12 +69,6 @@
     <t>METODOPAGO</t>
   </si>
   <si>
-    <t>ENTREGAINICIO</t>
-  </si>
-  <si>
-    <t>ENTREGAFINAL</t>
-  </si>
-  <si>
     <t>DESCUENTO</t>
   </si>
   <si>
@@ -120,12 +114,6 @@
     <t>PUE (pago en una sola exhibicion)</t>
   </si>
   <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
     <t>0</t>
   </si>
   <si>
@@ -150,9 +138,6 @@
     <t>$ 4,534.59</t>
   </si>
   <si>
-    <t>25</t>
-  </si>
-  <si>
     <t>MC. Jesús Alfredo Flores Osorio</t>
   </si>
   <si>
@@ -171,9 +156,6 @@
     <t>Por definir</t>
   </si>
   <si>
-    <t>5</t>
-  </si>
-  <si>
     <t>Luis Angel Lira</t>
   </si>
   <si>
@@ -210,9 +192,6 @@
     <t>PRUEBA FINAL 123</t>
   </si>
   <si>
-    <t>31</t>
-  </si>
-  <si>
     <t>$ 5,240.62</t>
   </si>
   <si>
@@ -228,9 +207,6 @@
     <t>FINABIEN-001-2025</t>
   </si>
   <si>
-    <t>3</t>
-  </si>
-  <si>
     <t>FO-SG-04-0888</t>
   </si>
   <si>
@@ -339,15 +315,6 @@
     <t>USD $ 0.00</t>
   </si>
   <si>
-    <t>$ 17,676.42</t>
-  </si>
-  <si>
-    <t>$ 2,828.23</t>
-  </si>
-  <si>
-    <t>$ 20,504.65</t>
-  </si>
-  <si>
     <t>$ 5,923.30</t>
   </si>
   <si>
@@ -357,12 +324,6 @@
     <t>$ 6,871.03</t>
   </si>
   <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
     <t>AVANTE20260908</t>
   </si>
   <si>
@@ -372,9 +333,6 @@
     <t>Efectivo</t>
   </si>
   <si>
-    <t>6</t>
-  </si>
-  <si>
     <t>CAD</t>
   </si>
   <si>
@@ -388,15 +346,25 @@
   </si>
   <si>
     <t>$ 1,318.28</t>
+  </si>
+  <si>
+    <t>FECHA_ENTREGA</t>
+  </si>
+  <si>
+    <t>DIAS_PAGO</t>
+  </si>
+  <si>
+    <t>MERCANCIA_RECIBIDA</t>
+  </si>
+  <si>
+    <t>PARCIAL</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="dd/MM/yyyy"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -432,7 +400,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -442,13 +410,11 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -784,32 +750,32 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45D375DD-15B7-4F53-9122-30FA48C9EA3E}">
   <dimension ref="A1:Y13"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" bestFit="true" customWidth="true" width="9.5" collapsed="true"/>
     <col min="2" max="2" bestFit="true" customWidth="true" width="13.0" collapsed="true"/>
     <col min="3" max="3" bestFit="true" customWidth="true" width="12.0" collapsed="true"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="11.125" collapsed="true"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="13.75" collapsed="true"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="11.09765625" collapsed="true"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="13.69921875" collapsed="true"/>
     <col min="6" max="7" bestFit="true" customWidth="true" width="11.0" collapsed="true"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" width="9.875" collapsed="true"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" width="9.8984375" collapsed="true"/>
     <col min="9" max="9" bestFit="true" customWidth="true" width="11.0" collapsed="true"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" width="11.625" collapsed="true"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" width="11.59765625" collapsed="true"/>
     <col min="11" max="11" bestFit="true" customWidth="true" width="13.0" collapsed="true"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" width="13.75" collapsed="true"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" width="13.125" collapsed="true"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" width="20.125" collapsed="true"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" width="13.69921875" collapsed="true"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" width="13.09765625" collapsed="true"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" width="20.09765625" collapsed="true"/>
     <col min="15" max="15" bestFit="true" customWidth="true" width="12.0" collapsed="true"/>
     <col min="16" max="16" bestFit="true" customWidth="true" width="11.0" collapsed="true"/>
     <col min="17" max="17" customWidth="true" width="13.5" collapsed="true"/>
-    <col min="18" max="18" customWidth="true" width="13.75" collapsed="true"/>
-    <col min="23" max="23" customWidth="true" width="15.75" collapsed="true"/>
-    <col min="24" max="24" bestFit="true" customWidth="true" width="19.875" collapsed="true"/>
+    <col min="18" max="18" customWidth="true" width="13.69921875" collapsed="true"/>
+    <col min="23" max="23" customWidth="true" width="15.69921875" collapsed="true"/>
+    <col min="24" max="24" bestFit="true" customWidth="true" width="19.8984375" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25">
       <c r="A1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -842,16 +808,16 @@
         <v>12</v>
       </c>
       <c r="L1" t="s">
+        <v>106</v>
+      </c>
+      <c r="M1" t="s">
+        <v>107</v>
+      </c>
+      <c r="N1" t="s">
         <v>13</v>
       </c>
-      <c r="M1" t="s">
+      <c r="O1" t="s">
         <v>14</v>
-      </c>
-      <c r="N1" t="s">
-        <v>15</v>
-      </c>
-      <c r="O1" t="s">
-        <v>16</v>
       </c>
       <c r="P1" t="s">
         <v>4</v>
@@ -860,28 +826,28 @@
         <v>5</v>
       </c>
       <c r="R1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="S1" t="s">
         <v>6</v>
       </c>
       <c r="T1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="U1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="V1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="W1" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="X1" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="Y1" t="s">
-        <v>89</v>
+        <v>108</v>
       </c>
     </row>
     <row r="2" spans="1:25">
@@ -892,138 +858,138 @@
         <v>46127</v>
       </c>
       <c r="C2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" t="s">
         <v>21</v>
       </c>
-      <c r="D2" t="s">
+      <c r="F2" t="s">
         <v>22</v>
       </c>
-      <c r="E2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H2" t="s">
         <v>24</v>
       </c>
-      <c r="G2" t="s">
+      <c r="I2" t="s">
         <v>25</v>
       </c>
-      <c r="H2" t="s">
+      <c r="J2" t="s">
         <v>26</v>
       </c>
-      <c r="I2" t="s">
+      <c r="K2" t="s">
         <v>27</v>
       </c>
-      <c r="J2" t="s">
+      <c r="L2" s="13">
+        <v>46266</v>
+      </c>
+      <c r="M2" s="13">
+        <v>46325.681932881947</v>
+      </c>
+      <c r="N2" t="s">
         <v>28</v>
       </c>
-      <c r="K2" t="s">
+      <c r="O2" t="s">
         <v>29</v>
       </c>
-      <c r="L2" t="s">
+      <c r="P2" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q2" t="s">
         <v>30</v>
       </c>
-      <c r="M2" t="s">
+      <c r="R2" t="s">
         <v>31</v>
       </c>
-      <c r="N2" t="s">
+      <c r="S2" t="s">
         <v>32</v>
       </c>
-      <c r="O2" t="s">
+      <c r="T2" t="s">
         <v>33</v>
       </c>
-      <c r="P2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q2" t="s">
+      <c r="U2" t="s">
         <v>34</v>
       </c>
-      <c r="R2" t="s">
+      <c r="V2" t="s">
         <v>35</v>
       </c>
-      <c r="S2" t="s">
-        <v>36</v>
-      </c>
-      <c r="T2" t="s">
-        <v>37</v>
-      </c>
-      <c r="U2" t="s">
-        <v>38</v>
-      </c>
-      <c r="V2" t="s">
-        <v>39</v>
-      </c>
       <c r="W2" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:25">
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" s="8">
+      <c r="B3" s="6">
         <v>46127</v>
       </c>
       <c r="C3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" t="s">
         <v>21</v>
       </c>
-      <c r="D3" t="s">
+      <c r="F3" t="s">
         <v>22</v>
       </c>
-      <c r="E3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F3" t="s">
-        <v>24</v>
-      </c>
       <c r="G3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H3" t="s">
+        <v>74</v>
+      </c>
+      <c r="I3" t="s">
         <v>25</v>
       </c>
-      <c r="H3" t="s">
+      <c r="J3" t="s">
+        <v>26</v>
+      </c>
+      <c r="K3" t="s">
+        <v>27</v>
+      </c>
+      <c r="L3" s="13">
+        <v>46266</v>
+      </c>
+      <c r="M3" s="13">
+        <v>46325.681932881947</v>
+      </c>
+      <c r="N3" t="s">
+        <v>75</v>
+      </c>
+      <c r="O3" t="s">
+        <v>29</v>
+      </c>
+      <c r="P3" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>36</v>
+      </c>
+      <c r="R3" t="s">
+        <v>31</v>
+      </c>
+      <c r="S3" t="s">
+        <v>32</v>
+      </c>
+      <c r="T3" t="s">
+        <v>76</v>
+      </c>
+      <c r="U3" t="s">
+        <v>77</v>
+      </c>
+      <c r="V3" t="s">
+        <v>78</v>
+      </c>
+      <c r="W3" t="s">
         <v>82</v>
-      </c>
-      <c r="I3" t="s">
-        <v>27</v>
-      </c>
-      <c r="J3" t="s">
-        <v>28</v>
-      </c>
-      <c r="K3" t="s">
-        <v>29</v>
-      </c>
-      <c r="L3" t="s">
-        <v>40</v>
-      </c>
-      <c r="M3" t="s">
-        <v>31</v>
-      </c>
-      <c r="N3" t="s">
-        <v>83</v>
-      </c>
-      <c r="O3" t="s">
-        <v>33</v>
-      </c>
-      <c r="P3" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>41</v>
-      </c>
-      <c r="R3" t="s">
-        <v>35</v>
-      </c>
-      <c r="S3" t="s">
-        <v>36</v>
-      </c>
-      <c r="T3" t="s">
-        <v>84</v>
-      </c>
-      <c r="U3" t="s">
-        <v>85</v>
-      </c>
-      <c r="V3" t="s">
-        <v>86</v>
-      </c>
-      <c r="W3" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="4" spans="1:25">
@@ -1034,679 +1000,682 @@
         <v>46127</v>
       </c>
       <c r="C4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" t="s">
         <v>21</v>
       </c>
-      <c r="D4" t="s">
+      <c r="F4" t="s">
         <v>22</v>
       </c>
-      <c r="E4" t="s">
-        <v>23</v>
-      </c>
-      <c r="F4" t="s">
-        <v>24</v>
-      </c>
       <c r="G4" t="s">
+        <v>23</v>
+      </c>
+      <c r="H4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I4" t="s">
         <v>25</v>
       </c>
-      <c r="H4" t="s">
-        <v>45</v>
-      </c>
-      <c r="I4" t="s">
+      <c r="J4" t="s">
+        <v>41</v>
+      </c>
+      <c r="K4" t="s">
         <v>27</v>
       </c>
-      <c r="J4" t="s">
-        <v>46</v>
-      </c>
-      <c r="K4" t="s">
+      <c r="L4" s="13">
+        <v>46266</v>
+      </c>
+      <c r="M4" s="13">
+        <v>46325.681932881947</v>
+      </c>
+      <c r="N4" t="s">
+        <v>28</v>
+      </c>
+      <c r="O4" t="s">
         <v>29</v>
       </c>
-      <c r="L4" t="s">
-        <v>47</v>
-      </c>
-      <c r="M4" t="s">
+      <c r="P4" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>42</v>
+      </c>
+      <c r="R4" t="s">
         <v>31</v>
       </c>
-      <c r="N4" t="s">
+      <c r="S4" t="s">
         <v>32</v>
       </c>
-      <c r="O4" t="s">
-        <v>33</v>
-      </c>
-      <c r="P4" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>48</v>
-      </c>
-      <c r="R4" t="s">
-        <v>35</v>
-      </c>
-      <c r="S4" t="s">
-        <v>36</v>
-      </c>
       <c r="T4" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="U4" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="V4" t="s">
-        <v>44</v>
+        <v>39</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="5" spans="1:25">
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="5">
         <v>46128</v>
       </c>
       <c r="C5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D5" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="E5" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="F5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G5" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H5" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="I5" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="J5" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="K5" t="s">
-        <v>53</v>
-      </c>
-      <c r="L5" t="s">
         <v>47</v>
       </c>
-      <c r="M5" t="s">
-        <v>31</v>
+      <c r="L5" s="13">
+        <v>46266</v>
+      </c>
+      <c r="M5" s="13">
+        <v>46325.681932881947</v>
       </c>
       <c r="N5" t="s">
+        <v>32</v>
+      </c>
+      <c r="O5" t="s">
+        <v>29</v>
+      </c>
+      <c r="P5" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q5" t="s">
         <v>36</v>
       </c>
-      <c r="O5" t="s">
-        <v>33</v>
-      </c>
-      <c r="P5" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>41</v>
-      </c>
       <c r="R5" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="S5" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="T5" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="U5" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="V5" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
     </row>
     <row r="6" spans="1:25">
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="4">
         <v>46128</v>
       </c>
       <c r="C6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D6" t="s">
+        <v>43</v>
+      </c>
+      <c r="E6" t="s">
+        <v>48</v>
+      </c>
+      <c r="F6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G6" t="s">
+        <v>23</v>
+      </c>
+      <c r="H6" t="s">
+        <v>67</v>
+      </c>
+      <c r="I6" t="s">
+        <v>45</v>
+      </c>
+      <c r="J6" t="s">
+        <v>26</v>
+      </c>
+      <c r="K6" t="s">
+        <v>47</v>
+      </c>
+      <c r="L6" s="13">
+        <v>46268</v>
+      </c>
+      <c r="M6" s="13">
+        <v>46325.681932881947</v>
+      </c>
+      <c r="N6" t="s">
+        <v>28</v>
+      </c>
+      <c r="O6" t="s">
+        <v>29</v>
+      </c>
+      <c r="P6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>36</v>
+      </c>
+      <c r="R6" t="s">
+        <v>31</v>
+      </c>
+      <c r="S6" t="s">
+        <v>32</v>
+      </c>
+      <c r="T6" t="s">
         <v>49</v>
       </c>
-      <c r="E6" t="s">
-        <v>54</v>
-      </c>
-      <c r="F6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G6" t="s">
-        <v>25</v>
-      </c>
-      <c r="H6" t="s">
-        <v>75</v>
-      </c>
-      <c r="I6" t="s">
+      <c r="U6" t="s">
+        <v>50</v>
+      </c>
+      <c r="V6" t="s">
         <v>51</v>
-      </c>
-      <c r="J6" t="s">
-        <v>28</v>
-      </c>
-      <c r="K6" t="s">
-        <v>53</v>
-      </c>
-      <c r="L6" t="s">
-        <v>47</v>
-      </c>
-      <c r="M6" t="s">
-        <v>47</v>
-      </c>
-      <c r="N6" t="s">
-        <v>32</v>
-      </c>
-      <c r="O6" t="s">
-        <v>33</v>
-      </c>
-      <c r="P6" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>41</v>
-      </c>
-      <c r="R6" t="s">
-        <v>35</v>
-      </c>
-      <c r="S6" t="s">
-        <v>36</v>
-      </c>
-      <c r="T6" t="s">
-        <v>55</v>
-      </c>
-      <c r="U6" t="s">
-        <v>56</v>
-      </c>
-      <c r="V6" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="7" spans="1:25">
       <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" s="13" t="n">
-        <v>46128.54262923611</v>
+      <c r="B7" s="9">
+        <v>46128.542629236108</v>
       </c>
       <c r="C7" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D7" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="E7" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="F7" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G7" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H7" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="I7" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="J7" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="K7" t="s">
-        <v>53</v>
-      </c>
-      <c r="L7" t="s">
-        <v>109</v>
-      </c>
-      <c r="M7" t="s">
         <v>47</v>
       </c>
+      <c r="L7" s="13">
+        <v>46266</v>
+      </c>
+      <c r="M7" s="13">
+        <v>46325.681932881947</v>
+      </c>
       <c r="N7" t="s">
+        <v>28</v>
+      </c>
+      <c r="O7" t="s">
+        <v>29</v>
+      </c>
+      <c r="P7" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>36</v>
+      </c>
+      <c r="R7" t="s">
+        <v>31</v>
+      </c>
+      <c r="S7" t="s">
         <v>32</v>
       </c>
-      <c r="O7" t="s">
-        <v>33</v>
-      </c>
-      <c r="P7" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>41</v>
-      </c>
-      <c r="R7" t="s">
-        <v>35</v>
-      </c>
-      <c r="S7" t="s">
-        <v>36</v>
-      </c>
       <c r="T7" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="U7" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="V7" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
     </row>
     <row r="8" spans="1:25">
       <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8" s="4">
+      <c r="B8" s="3">
         <v>46128.551586458336</v>
       </c>
       <c r="C8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D8" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="E8" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="F8" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G8" t="s">
+        <v>23</v>
+      </c>
+      <c r="H8" t="s">
+        <v>58</v>
+      </c>
+      <c r="I8" t="s">
         <v>25</v>
       </c>
-      <c r="H8" t="s">
-        <v>65</v>
-      </c>
-      <c r="I8" t="s">
+      <c r="J8" t="s">
+        <v>26</v>
+      </c>
+      <c r="K8" t="s">
         <v>27</v>
       </c>
-      <c r="J8" t="s">
+      <c r="L8" s="13">
+        <v>46266</v>
+      </c>
+      <c r="M8" s="13">
+        <v>46325.681932881947</v>
+      </c>
+      <c r="N8" t="s">
         <v>28</v>
       </c>
-      <c r="K8" t="s">
+      <c r="O8" t="s">
         <v>29</v>
       </c>
-      <c r="L8" t="s">
-        <v>66</v>
-      </c>
-      <c r="M8" t="s">
-        <v>47</v>
-      </c>
-      <c r="N8" t="s">
+      <c r="P8" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>36</v>
+      </c>
+      <c r="R8" t="s">
+        <v>31</v>
+      </c>
+      <c r="S8" t="s">
         <v>32</v>
       </c>
-      <c r="O8" t="s">
-        <v>33</v>
-      </c>
-      <c r="P8" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>41</v>
-      </c>
-      <c r="R8" t="s">
-        <v>35</v>
-      </c>
-      <c r="S8" t="s">
-        <v>36</v>
-      </c>
       <c r="T8" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="U8" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="V8" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9" spans="1:25">
       <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9" s="5">
+      <c r="B9" s="12">
         <v>46129.476984456021</v>
       </c>
       <c r="C9" t="s">
+        <v>59</v>
+      </c>
+      <c r="D9" t="s">
+        <v>60</v>
+      </c>
+      <c r="E9" t="s">
+        <v>61</v>
+      </c>
+      <c r="F9" t="s">
+        <v>22</v>
+      </c>
+      <c r="G9" t="s">
+        <v>23</v>
+      </c>
+      <c r="H9" t="s">
+        <v>62</v>
+      </c>
+      <c r="I9" t="s">
+        <v>25</v>
+      </c>
+      <c r="J9" t="s">
+        <v>26</v>
+      </c>
+      <c r="K9" t="s">
+        <v>27</v>
+      </c>
+      <c r="L9" s="13">
+        <v>46266</v>
+      </c>
+      <c r="M9" s="13">
+        <v>46325.681932881947</v>
+      </c>
+      <c r="N9" t="s">
+        <v>28</v>
+      </c>
+      <c r="O9" t="s">
+        <v>29</v>
+      </c>
+      <c r="P9" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>36</v>
+      </c>
+      <c r="R9" t="s">
+        <v>31</v>
+      </c>
+      <c r="S9" t="s">
+        <v>32</v>
+      </c>
+      <c r="T9" t="s">
+        <v>64</v>
+      </c>
+      <c r="U9" t="s">
+        <v>65</v>
+      </c>
+      <c r="V9" t="s">
+        <v>66</v>
+      </c>
+      <c r="W9" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" s="7">
+        <v>46269.711945787036</v>
+      </c>
+      <c r="C10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10" t="s">
+        <v>83</v>
+      </c>
+      <c r="E10" t="s">
+        <v>84</v>
+      </c>
+      <c r="F10" t="s">
+        <v>22</v>
+      </c>
+      <c r="G10" t="s">
+        <v>23</v>
+      </c>
+      <c r="H10" t="s">
+        <v>85</v>
+      </c>
+      <c r="I10" t="s">
+        <v>45</v>
+      </c>
+      <c r="J10" t="s">
+        <v>26</v>
+      </c>
+      <c r="K10" t="s">
+        <v>47</v>
+      </c>
+      <c r="L10" s="13">
+        <v>46270</v>
+      </c>
+      <c r="M10" s="13">
+        <v>46325.681932881947</v>
+      </c>
+      <c r="N10" t="s">
+        <v>28</v>
+      </c>
+      <c r="O10" t="s">
+        <v>29</v>
+      </c>
+      <c r="P10" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>36</v>
+      </c>
+      <c r="R10" t="s">
+        <v>31</v>
+      </c>
+      <c r="S10" t="s">
+        <v>32</v>
+      </c>
+      <c r="T10" t="s">
+        <v>87</v>
+      </c>
+      <c r="U10" t="s">
+        <v>88</v>
+      </c>
+      <c r="V10" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" s="8">
+        <v>46272.439317673612</v>
+      </c>
+      <c r="C11" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" t="s">
+        <v>90</v>
+      </c>
+      <c r="E11" t="s">
+        <v>61</v>
+      </c>
+      <c r="F11" t="s">
+        <v>22</v>
+      </c>
+      <c r="G11" t="s">
+        <v>36</v>
+      </c>
+      <c r="H11" t="s">
+        <v>24</v>
+      </c>
+      <c r="I11" t="s">
+        <v>25</v>
+      </c>
+      <c r="J11" t="s">
+        <v>26</v>
+      </c>
+      <c r="K11" t="s">
+        <v>27</v>
+      </c>
+      <c r="L11" s="13">
+        <v>46266</v>
+      </c>
+      <c r="M11" s="13">
+        <v>46325.681932881947</v>
+      </c>
+      <c r="N11" t="s">
+        <v>63</v>
+      </c>
+      <c r="O11" t="s">
+        <v>91</v>
+      </c>
+      <c r="P11" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>36</v>
+      </c>
+      <c r="R11" t="s">
+        <v>69</v>
+      </c>
+      <c r="S11" t="s">
+        <v>92</v>
+      </c>
+      <c r="T11" t="s">
+        <v>93</v>
+      </c>
+      <c r="U11" t="s">
+        <v>94</v>
+      </c>
+      <c r="V11" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" s="10">
+        <v>46128</v>
+      </c>
+      <c r="C12" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" t="s">
+        <v>43</v>
+      </c>
+      <c r="E12" t="s">
+        <v>48</v>
+      </c>
+      <c r="F12" t="s">
+        <v>22</v>
+      </c>
+      <c r="G12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H12" t="s">
         <v>67</v>
       </c>
-      <c r="D9" t="s">
-        <v>68</v>
-      </c>
-      <c r="E9" t="s">
-        <v>69</v>
-      </c>
-      <c r="F9" t="s">
-        <v>24</v>
-      </c>
-      <c r="G9" t="s">
+      <c r="I12" t="s">
+        <v>45</v>
+      </c>
+      <c r="J12" t="s">
+        <v>26</v>
+      </c>
+      <c r="K12" t="s">
+        <v>47</v>
+      </c>
+      <c r="L12" s="13">
+        <v>46266</v>
+      </c>
+      <c r="M12" s="13">
+        <v>46325.681932881947</v>
+      </c>
+      <c r="N12" t="s">
+        <v>86</v>
+      </c>
+      <c r="O12" t="s">
+        <v>29</v>
+      </c>
+      <c r="P12" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>36</v>
+      </c>
+      <c r="R12" t="s">
+        <v>31</v>
+      </c>
+      <c r="S12" t="s">
+        <v>32</v>
+      </c>
+      <c r="T12" t="s">
+        <v>95</v>
+      </c>
+      <c r="U12" t="s">
+        <v>96</v>
+      </c>
+      <c r="V12" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" s="11">
+        <v>46273.664973483799</v>
+      </c>
+      <c r="C13" t="s">
+        <v>19</v>
+      </c>
+      <c r="D13" t="s">
+        <v>98</v>
+      </c>
+      <c r="E13" t="s">
+        <v>52</v>
+      </c>
+      <c r="F13" t="s">
+        <v>22</v>
+      </c>
+      <c r="G13" t="s">
+        <v>36</v>
+      </c>
+      <c r="H13" t="s">
+        <v>99</v>
+      </c>
+      <c r="I13" t="s">
         <v>25</v>
       </c>
-      <c r="H9" t="s">
-        <v>70</v>
-      </c>
-      <c r="I9" t="s">
-        <v>27</v>
-      </c>
-      <c r="J9" t="s">
+      <c r="J13" t="s">
+        <v>100</v>
+      </c>
+      <c r="K13" t="s">
+        <v>47</v>
+      </c>
+      <c r="L13" s="13">
+        <v>46274</v>
+      </c>
+      <c r="M13" s="13">
+        <v>46325.681932881947</v>
+      </c>
+      <c r="N13" t="s">
         <v>28</v>
       </c>
-      <c r="K9" t="s">
+      <c r="O13" t="s">
         <v>29</v>
       </c>
-      <c r="L9" t="s">
-        <v>47</v>
-      </c>
-      <c r="M9" t="s">
-        <v>71</v>
-      </c>
-      <c r="N9" t="s">
-        <v>32</v>
-      </c>
-      <c r="O9" t="s">
-        <v>33</v>
-      </c>
-      <c r="P9" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q9" t="s">
-        <v>41</v>
-      </c>
-      <c r="R9" t="s">
-        <v>35</v>
-      </c>
-      <c r="S9" t="s">
+      <c r="P13" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q13" t="s">
         <v>36</v>
       </c>
-      <c r="T9" t="s">
-        <v>72</v>
-      </c>
-      <c r="U9" t="s">
-        <v>73</v>
-      </c>
-      <c r="V9" t="s">
-        <v>74</v>
-      </c>
-      <c r="W9" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>9.0</v>
-      </c>
-      <c r="B10" t="n" s="9">
-        <v>46269.711945787036</v>
-      </c>
-      <c r="C10" t="s">
-        <v>21</v>
-      </c>
-      <c r="D10" t="s">
-        <v>91</v>
-      </c>
-      <c r="E10" t="s">
-        <v>92</v>
-      </c>
-      <c r="F10" t="s">
-        <v>24</v>
-      </c>
-      <c r="G10" t="s">
-        <v>25</v>
-      </c>
-      <c r="H10" t="s">
-        <v>93</v>
-      </c>
-      <c r="I10" t="s">
-        <v>51</v>
-      </c>
-      <c r="J10" t="s">
-        <v>28</v>
-      </c>
-      <c r="K10" t="s">
-        <v>53</v>
-      </c>
-      <c r="L10" t="s">
-        <v>94</v>
-      </c>
-      <c r="M10" t="s">
-        <v>31</v>
-      </c>
-      <c r="N10" t="s">
-        <v>32</v>
-      </c>
-      <c r="O10" t="s">
-        <v>33</v>
-      </c>
-      <c r="P10" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>41</v>
-      </c>
-      <c r="R10" t="s">
-        <v>35</v>
-      </c>
-      <c r="S10" t="s">
-        <v>36</v>
-      </c>
-      <c r="T10" t="s">
-        <v>95</v>
-      </c>
-      <c r="U10" t="s">
-        <v>96</v>
-      </c>
-      <c r="V10" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>10.0</v>
-      </c>
-      <c r="B11" t="n" s="10">
-        <v>46272.43931767361</v>
-      </c>
-      <c r="C11" t="s">
-        <v>21</v>
-      </c>
-      <c r="D11" t="s">
-        <v>98</v>
-      </c>
-      <c r="E11" t="s">
-        <v>69</v>
-      </c>
-      <c r="F11" t="s">
-        <v>24</v>
-      </c>
-      <c r="G11" t="s">
-        <v>41</v>
-      </c>
-      <c r="H11" t="s">
-        <v>26</v>
-      </c>
-      <c r="I11" t="s">
-        <v>27</v>
-      </c>
-      <c r="J11" t="s">
-        <v>28</v>
-      </c>
-      <c r="K11" t="s">
-        <v>29</v>
-      </c>
-      <c r="L11" t="s">
-        <v>66</v>
-      </c>
-      <c r="M11" t="s">
-        <v>47</v>
-      </c>
-      <c r="N11" t="s">
-        <v>71</v>
-      </c>
-      <c r="O11" t="s">
-        <v>99</v>
-      </c>
-      <c r="P11" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>41</v>
-      </c>
-      <c r="R11" t="s">
-        <v>77</v>
-      </c>
-      <c r="S11" t="s">
-        <v>100</v>
-      </c>
-      <c r="T11" t="s">
+      <c r="R13" t="s">
         <v>101</v>
       </c>
-      <c r="U11" t="s">
+      <c r="S13" t="s">
         <v>102</v>
       </c>
-      <c r="V11" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>11.0</v>
-      </c>
-      <c r="B12" t="n" s="14">
-        <v>46128.0</v>
-      </c>
-      <c r="C12" t="s">
-        <v>21</v>
-      </c>
-      <c r="D12" t="s">
-        <v>49</v>
-      </c>
-      <c r="E12" t="s">
-        <v>54</v>
-      </c>
-      <c r="F12" t="s">
-        <v>24</v>
-      </c>
-      <c r="G12" t="s">
-        <v>25</v>
-      </c>
-      <c r="H12" t="s">
-        <v>75</v>
-      </c>
-      <c r="I12" t="s">
-        <v>51</v>
-      </c>
-      <c r="J12" t="s">
-        <v>28</v>
-      </c>
-      <c r="K12" t="s">
-        <v>53</v>
-      </c>
-      <c r="L12" t="s">
-        <v>47</v>
-      </c>
-      <c r="M12" t="s">
-        <v>110</v>
-      </c>
-      <c r="N12" t="s">
-        <v>94</v>
-      </c>
-      <c r="O12" t="s">
-        <v>33</v>
-      </c>
-      <c r="P12" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>41</v>
-      </c>
-      <c r="R12" t="s">
-        <v>35</v>
-      </c>
-      <c r="S12" t="s">
-        <v>36</v>
-      </c>
-      <c r="T12" t="s">
-        <v>106</v>
-      </c>
-      <c r="U12" t="s">
-        <v>107</v>
-      </c>
-      <c r="V12" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>12.0</v>
-      </c>
-      <c r="B13" t="n" s="15">
-        <v>46273.6649734838</v>
-      </c>
-      <c r="C13" t="s">
-        <v>21</v>
-      </c>
-      <c r="D13" t="s">
-        <v>111</v>
-      </c>
-      <c r="E13" t="s">
-        <v>58</v>
-      </c>
-      <c r="F13" t="s">
-        <v>24</v>
-      </c>
-      <c r="G13" t="s">
-        <v>41</v>
-      </c>
-      <c r="H13" t="s">
-        <v>112</v>
-      </c>
-      <c r="I13" t="s">
-        <v>27</v>
-      </c>
-      <c r="J13" t="s">
-        <v>113</v>
-      </c>
-      <c r="K13" t="s">
-        <v>53</v>
-      </c>
-      <c r="L13" t="s">
-        <v>66</v>
-      </c>
-      <c r="M13" t="s">
-        <v>114</v>
-      </c>
-      <c r="N13" t="s">
-        <v>32</v>
-      </c>
-      <c r="O13" t="s">
-        <v>33</v>
-      </c>
-      <c r="P13" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>41</v>
-      </c>
-      <c r="R13" t="s">
-        <v>115</v>
-      </c>
-      <c r="S13" t="s">
-        <v>116</v>
-      </c>
       <c r="T13" t="s">
-        <v>117</v>
+        <v>103</v>
       </c>
       <c r="U13" t="s">
-        <v>118</v>
+        <v>104</v>
       </c>
       <c r="V13" t="s">
-        <v>119</v>
+        <v>105</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/java/com/mycompany/ocxrst/BASES/REGISTROC.xlsx
+++ b/src/main/java/com/mycompany/ocxrst/BASES/REGISTROC.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="76">
   <si>
     <t>FECHA</t>
   </si>
@@ -235,6 +235,27 @@
   </si>
   <si>
     <t>$ 11,607.25</t>
+  </si>
+  <si>
+    <t>-3</t>
+  </si>
+  <si>
+    <t>PRUEBA DE OBSERVACIONES</t>
+  </si>
+  <si>
+    <t>PRUEBASEPTIEMBRE</t>
+  </si>
+  <si>
+    <t>PENDIENTE</t>
+  </si>
+  <si>
+    <t>$ 8,234.63</t>
+  </si>
+  <si>
+    <t>$ 1,317.54</t>
+  </si>
+  <si>
+    <t>$ 9,552.17</t>
   </si>
 </sst>
 </file>
@@ -279,11 +300,38 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
@@ -630,7 +678,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45D375DD-15B7-4F53-9122-30FA48C9EA3E}">
-  <dimension ref="A1:Z5"/>
+  <dimension ref="A1:Z6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" bestFit="true" customWidth="true" width="9.5" collapsed="true"/>
@@ -980,7 +1028,7 @@
       <c r="A5" t="n">
         <v>4.0</v>
       </c>
-      <c r="B5" t="n" s="13">
+      <c r="B5" t="n" s="31">
         <v>46306.72483490741</v>
       </c>
       <c r="C5" t="s">
@@ -999,7 +1047,7 @@
         <v>29</v>
       </c>
       <c r="H5" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="I5" t="s">
         <v>31</v>
@@ -1010,10 +1058,10 @@
       <c r="K5" t="s">
         <v>33</v>
       </c>
-      <c r="L5" t="n" s="14">
-        <v>46279.72541641204</v>
-      </c>
-      <c r="M5" t="n" s="15">
+      <c r="L5" t="n" s="32">
+        <v>46279.0</v>
+      </c>
+      <c r="M5" t="n" s="33">
         <v>46279.0</v>
       </c>
       <c r="N5" t="s">
@@ -1042,6 +1090,95 @@
       </c>
       <c r="V5" t="s">
         <v>68</v>
+      </c>
+      <c r="W5" t="s">
+        <v>68</v>
+      </c>
+      <c r="X5" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="B6" t="n" s="40">
+        <v>46306.72483490741</v>
+      </c>
+      <c r="C6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" t="s">
+        <v>64</v>
+      </c>
+      <c r="F6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G6" t="s">
+        <v>29</v>
+      </c>
+      <c r="H6" t="s">
+        <v>71</v>
+      </c>
+      <c r="I6" t="s">
+        <v>31</v>
+      </c>
+      <c r="J6" t="s">
+        <v>32</v>
+      </c>
+      <c r="K6" t="s">
+        <v>33</v>
+      </c>
+      <c r="L6" t="n" s="41">
+        <v>46293.0</v>
+      </c>
+      <c r="M6" t="n" s="42">
+        <v>46295.0</v>
+      </c>
+      <c r="N6" t="s">
+        <v>34</v>
+      </c>
+      <c r="O6" t="s">
+        <v>35</v>
+      </c>
+      <c r="P6" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>37</v>
+      </c>
+      <c r="R6" t="s">
+        <v>38</v>
+      </c>
+      <c r="S6" t="s">
+        <v>39</v>
+      </c>
+      <c r="T6" t="s">
+        <v>73</v>
+      </c>
+      <c r="U6" t="s">
+        <v>74</v>
+      </c>
+      <c r="V6" t="s">
+        <v>75</v>
+      </c>
+      <c r="W6" t="s">
+        <v>34</v>
+      </c>
+      <c r="X6" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/java/com/mycompany/ocxrst/BASES/REGISTROC.xlsx
+++ b/src/main/java/com/mycompany/ocxrst/BASES/REGISTROC.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OCXRST\OrdendeComprasRST\src\main\java\com\mycompany\ocxrst\BASES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{799262D4-2FD9-4003-8B74-F753852CA118}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D755DDC9-CFF7-4F80-83BF-0B8B118195A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{1A5C3FBD-CC1E-4D2B-B7AC-82264016413D}"/>
+    <workbookView xWindow="3024" yWindow="2304" windowWidth="16740" windowHeight="9372" xr2:uid="{1A5C3FBD-CC1E-4D2B-B7AC-82264016413D}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -20,15 +20,12 @@
     <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="61">
   <si>
     <t>FECHA</t>
   </si>
@@ -108,39 +105,39 @@
     <t>FO-SG-04-00</t>
   </si>
   <si>
-    <t>AVANTE20260911</t>
-  </si>
-  <si>
-    <t>bimb26</t>
+    <t>AVANTE20260924</t>
+  </si>
+  <si>
+    <t>mode09</t>
   </si>
   <si>
     <t>G03 - Gastos en general</t>
   </si>
   <si>
+    <t>Luis Angel Lira</t>
+  </si>
+  <si>
+    <t>FINANCIERA</t>
+  </si>
+  <si>
+    <t>Contado</t>
+  </si>
+  <si>
+    <t>Transferencia Electrónica</t>
+  </si>
+  <si>
+    <t>PUE (pago en una sola exhibicion)</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>SI</t>
+  </si>
+  <si>
     <t>María Luisa Martínez Morales</t>
   </si>
   <si>
-    <t>PRUEBA</t>
-  </si>
-  <si>
-    <t>Contado</t>
-  </si>
-  <si>
-    <t>Transferencia Electrónica</t>
-  </si>
-  <si>
-    <t>PPD (pago por partes)</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>SI</t>
-  </si>
-  <si>
-    <t>Luis Angel Lira</t>
-  </si>
-  <si>
     <t>MC. Jesús Alfredo Flores Osorio</t>
   </si>
   <si>
@@ -150,122 +147,78 @@
     <t/>
   </si>
   <si>
-    <t>$ 8,389.90</t>
-  </si>
-  <si>
-    <t>$ 1,342.38</t>
-  </si>
-  <si>
-    <t>$ 9,732.28</t>
+    <t>$ 19,729.84</t>
+  </si>
+  <si>
+    <t>$ 3,156.77</t>
+  </si>
+  <si>
+    <t>$ 22,886.61</t>
   </si>
   <si>
     <t>PARCIAL</t>
   </si>
   <si>
-    <t>PENDIENTE PAGO Y MERCANCIA</t>
+    <t>$ 11,607.25</t>
   </si>
   <si>
     <t>PENDIENTE DE MERCANCIA</t>
   </si>
   <si>
+    <t>PENDIENTE DE PAGO</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>herd05</t>
+  </si>
+  <si>
+    <t>PRUEBA ESTATUS</t>
+  </si>
+  <si>
+    <t>Crédito</t>
+  </si>
+  <si>
+    <t>Efectivo</t>
+  </si>
+  <si>
+    <t>$ 8,184.15</t>
+  </si>
+  <si>
+    <t>$ 1,309.46</t>
+  </si>
+  <si>
+    <t>$ 9,493.61</t>
+  </si>
+  <si>
+    <t>PENDIENTE</t>
+  </si>
+  <si>
+    <t>XXXX</t>
+  </si>
+  <si>
     <t>FINALIZADO</t>
   </si>
   <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>coca03</t>
-  </si>
-  <si>
-    <t>PRUEBA2</t>
-  </si>
-  <si>
-    <t>$ 3,609.17</t>
-  </si>
-  <si>
-    <t>$ 577.47</t>
-  </si>
-  <si>
-    <t>$ 4,186.64</t>
-  </si>
-  <si>
-    <t>PENDIENTE DE PAGO</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>sabri02</t>
-  </si>
-  <si>
-    <t>PRUEBA 3</t>
-  </si>
-  <si>
-    <t>Crédito</t>
-  </si>
-  <si>
-    <t>$ 5,743.01</t>
-  </si>
-  <si>
-    <t>$ 918.88</t>
-  </si>
-  <si>
-    <t>$ 6,661.89</t>
-  </si>
-  <si>
-    <t>$ 2,157.00</t>
-  </si>
-  <si>
-    <t>$ 4,314.00</t>
-  </si>
-  <si>
-    <t>$ 6,471.00</t>
-  </si>
-  <si>
-    <t>nest04</t>
-  </si>
-  <si>
-    <t>PRUEBANOT</t>
-  </si>
-  <si>
-    <t>$ 10,006.25</t>
-  </si>
-  <si>
-    <t>$ 1,601.00</t>
-  </si>
-  <si>
-    <t>$ 11,607.25</t>
-  </si>
-  <si>
-    <t>-3</t>
-  </si>
-  <si>
-    <t>PRUEBA DE OBSERVACIONES</t>
-  </si>
-  <si>
-    <t>PRUEBASEPTIEMBRE</t>
-  </si>
-  <si>
-    <t>PENDIENTE</t>
-  </si>
-  <si>
-    <t>$ 8,234.63</t>
-  </si>
-  <si>
-    <t>$ 1,317.54</t>
-  </si>
-  <si>
-    <t>$ 9,552.17</t>
+    <t>-6</t>
+  </si>
+  <si>
+    <t>AVANTE 11,607.25</t>
+  </si>
+  <si>
+    <t>1</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="dd/MM/yyyy"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
+    <numFmt numFmtId="165" formatCode="dd/MM/yyyy"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -300,50 +253,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -678,33 +593,33 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45D375DD-15B7-4F53-9122-30FA48C9EA3E}">
-  <dimension ref="A1:Z6"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.8"/>
+  <dimension ref="A1:Z4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="9.5" collapsed="true"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="9.44140625" collapsed="true"/>
     <col min="2" max="2" bestFit="true" customWidth="true" width="13.0" collapsed="true"/>
     <col min="3" max="3" bestFit="true" customWidth="true" width="12.0" collapsed="true"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="11.09765625" collapsed="true"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="13.69921875" collapsed="true"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="11.109375" collapsed="true"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="13.6640625" collapsed="true"/>
     <col min="6" max="7" bestFit="true" customWidth="true" width="11.0" collapsed="true"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" width="9.8984375" collapsed="true"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" width="9.88671875" collapsed="true"/>
     <col min="9" max="9" bestFit="true" customWidth="true" width="11.0" collapsed="true"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" width="11.59765625" collapsed="true"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" width="28.796875" collapsed="true"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" width="13.69921875" collapsed="true"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" width="13.09765625" collapsed="true"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" width="20.09765625" collapsed="true"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" width="11.5546875" collapsed="true"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" width="28.77734375" collapsed="true"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" width="13.6640625" collapsed="true"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" width="13.109375" collapsed="true"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" width="20.109375" collapsed="true"/>
     <col min="15" max="15" bestFit="true" customWidth="true" width="12.0" collapsed="true"/>
     <col min="16" max="16" bestFit="true" customWidth="true" width="11.0" collapsed="true"/>
-    <col min="17" max="17" customWidth="true" width="13.5" collapsed="true"/>
-    <col min="18" max="18" customWidth="true" width="13.69921875" collapsed="true"/>
-    <col min="23" max="23" customWidth="true" width="15.69921875" collapsed="true"/>
-    <col min="24" max="24" bestFit="true" customWidth="true" width="19.8984375" collapsed="true"/>
-    <col min="25" max="25" bestFit="true" customWidth="true" width="20.69921875" collapsed="true"/>
-    <col min="26" max="26" bestFit="true" customWidth="true" width="27.796875" collapsed="true"/>
+    <col min="17" max="17" customWidth="true" width="13.44140625" collapsed="true"/>
+    <col min="18" max="18" customWidth="true" width="13.6640625" collapsed="true"/>
+    <col min="23" max="23" customWidth="true" width="15.6640625" collapsed="true"/>
+    <col min="24" max="24" bestFit="true" customWidth="true" width="19.88671875" collapsed="true"/>
+    <col min="25" max="25" bestFit="true" customWidth="true" width="20.6640625" collapsed="true"/>
+    <col min="26" max="26" bestFit="true" customWidth="true" width="27.77734375" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26">
+    <row r="1" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>16</v>
       </c>
@@ -784,12 +699,12 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:26">
+    <row r="2" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" s="1">
-        <v>46276.458858587961</v>
+        <v>46289.517945069441</v>
       </c>
       <c r="C2" t="s">
         <v>25</v>
@@ -818,11 +733,11 @@
       <c r="K2" t="s">
         <v>33</v>
       </c>
-      <c r="L2" s="2">
-        <v>46295.459460613427</v>
-      </c>
-      <c r="M2" s="3">
-        <v>46295.459527569445</v>
+      <c r="L2" s="1">
+        <v>46295.518404016206</v>
+      </c>
+      <c r="M2" s="1">
+        <v>46294.518495532408</v>
       </c>
       <c r="N2" t="s">
         <v>34</v>
@@ -855,7 +770,7 @@
         <v>42</v>
       </c>
       <c r="X2" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="Y2" t="s">
         <v>35</v>
@@ -864,12 +779,12 @@
         <v>47</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="B3" t="n" s="4">
-        <v>46254.47988886574</v>
+    <row r="3" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1">
+        <v>46289.517945069441</v>
       </c>
       <c r="C3" t="s">
         <v>25</v>
@@ -878,16 +793,16 @@
         <v>26</v>
       </c>
       <c r="E3" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="F3" t="s">
         <v>28</v>
       </c>
       <c r="G3" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="H3" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="I3" t="s">
         <v>31</v>
@@ -898,11 +813,11 @@
       <c r="K3" t="s">
         <v>33</v>
       </c>
-      <c r="L3" t="n" s="5">
-        <v>46279.48019362269</v>
-      </c>
-      <c r="M3" t="n" s="6">
-        <v>46295.48062410879</v>
+      <c r="L3" s="1">
+        <v>46295</v>
+      </c>
+      <c r="M3" s="1">
+        <v>46294</v>
       </c>
       <c r="N3" t="s">
         <v>34</v>
@@ -911,7 +826,7 @@
         <v>35</v>
       </c>
       <c r="P3" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="Q3" t="s">
         <v>37</v>
@@ -923,33 +838,33 @@
         <v>39</v>
       </c>
       <c r="T3" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="U3" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="V3" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="W3" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="X3" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="Y3" t="s">
         <v>35</v>
       </c>
       <c r="Z3" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>3.0</v>
       </c>
-      <c r="B4" t="n" s="10">
-        <v>46266.50434375</v>
+      <c r="B4" t="n" s="2">
+        <v>46282.58864228009</v>
       </c>
       <c r="C4" t="s">
         <v>25</v>
@@ -958,31 +873,31 @@
         <v>26</v>
       </c>
       <c r="E4" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="F4" t="s">
         <v>28</v>
       </c>
       <c r="G4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H4" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="I4" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="J4" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="K4" t="s">
         <v>33</v>
       </c>
-      <c r="L4" t="n" s="11">
-        <v>46279.0</v>
-      </c>
-      <c r="M4" t="n" s="12">
-        <v>46283.0</v>
+      <c r="L4" t="n" s="3">
+        <v>46283.588922546296</v>
+      </c>
+      <c r="M4" t="n" s="4">
+        <v>46289.58924150463</v>
       </c>
       <c r="N4" t="s">
         <v>34</v>
@@ -994,7 +909,7 @@
         <v>37</v>
       </c>
       <c r="Q4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R4" t="s">
         <v>38</v>
@@ -1003,182 +918,25 @@
         <v>39</v>
       </c>
       <c r="T4" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="U4" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="V4" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="W4" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="X4" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="Y4" t="s">
         <v>35</v>
       </c>
       <c r="Z4" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>4.0</v>
-      </c>
-      <c r="B5" t="n" s="31">
-        <v>46306.72483490741</v>
-      </c>
-      <c r="C5" t="s">
-        <v>25</v>
-      </c>
-      <c r="D5" t="s">
-        <v>26</v>
-      </c>
-      <c r="E5" t="s">
-        <v>64</v>
-      </c>
-      <c r="F5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G5" t="s">
-        <v>29</v>
-      </c>
-      <c r="H5" t="s">
-        <v>71</v>
-      </c>
-      <c r="I5" t="s">
-        <v>31</v>
-      </c>
-      <c r="J5" t="s">
-        <v>32</v>
-      </c>
-      <c r="K5" t="s">
-        <v>33</v>
-      </c>
-      <c r="L5" t="n" s="32">
-        <v>46279.0</v>
-      </c>
-      <c r="M5" t="n" s="33">
-        <v>46279.0</v>
-      </c>
-      <c r="N5" t="s">
-        <v>34</v>
-      </c>
-      <c r="O5" t="s">
-        <v>35</v>
-      </c>
-      <c r="P5" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>37</v>
-      </c>
-      <c r="R5" t="s">
-        <v>38</v>
-      </c>
-      <c r="S5" t="s">
-        <v>39</v>
-      </c>
-      <c r="T5" t="s">
-        <v>66</v>
-      </c>
-      <c r="U5" t="s">
-        <v>67</v>
-      </c>
-      <c r="V5" t="s">
-        <v>68</v>
-      </c>
-      <c r="W5" t="s">
-        <v>68</v>
-      </c>
-      <c r="X5" t="s">
-        <v>45</v>
-      </c>
-      <c r="Y5" t="s">
-        <v>43</v>
-      </c>
-      <c r="Z5" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="B6" t="n" s="40">
-        <v>46306.72483490741</v>
-      </c>
-      <c r="C6" t="s">
-        <v>25</v>
-      </c>
-      <c r="D6" t="s">
-        <v>26</v>
-      </c>
-      <c r="E6" t="s">
-        <v>64</v>
-      </c>
-      <c r="F6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G6" t="s">
-        <v>29</v>
-      </c>
-      <c r="H6" t="s">
-        <v>71</v>
-      </c>
-      <c r="I6" t="s">
-        <v>31</v>
-      </c>
-      <c r="J6" t="s">
-        <v>32</v>
-      </c>
-      <c r="K6" t="s">
-        <v>33</v>
-      </c>
-      <c r="L6" t="n" s="41">
-        <v>46293.0</v>
-      </c>
-      <c r="M6" t="n" s="42">
-        <v>46295.0</v>
-      </c>
-      <c r="N6" t="s">
-        <v>34</v>
-      </c>
-      <c r="O6" t="s">
-        <v>35</v>
-      </c>
-      <c r="P6" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>37</v>
-      </c>
-      <c r="R6" t="s">
-        <v>38</v>
-      </c>
-      <c r="S6" t="s">
-        <v>39</v>
-      </c>
-      <c r="T6" t="s">
-        <v>73</v>
-      </c>
-      <c r="U6" t="s">
-        <v>74</v>
-      </c>
-      <c r="V6" t="s">
-        <v>75</v>
-      </c>
-      <c r="W6" t="s">
-        <v>34</v>
-      </c>
-      <c r="X6" t="s">
-        <v>72</v>
-      </c>
-      <c r="Y6" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/java/com/mycompany/ocxrst/BASES/REGISTROC.xlsx
+++ b/src/main/java/com/mycompany/ocxrst/BASES/REGISTROC.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OCXRST\OrdendeComprasRST\src\main\java\com\mycompany\ocxrst\BASES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D755DDC9-CFF7-4F80-83BF-0B8B118195A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67515AAC-73E5-466E-8341-5648D682CEC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3024" yWindow="2304" windowWidth="16740" windowHeight="9372" xr2:uid="{1A5C3FBD-CC1E-4D2B-B7AC-82264016413D}"/>
+    <workbookView xWindow="612" yWindow="-108" windowWidth="22536" windowHeight="13176" xr2:uid="{1A5C3FBD-CC1E-4D2B-B7AC-82264016413D}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="50">
   <si>
     <t>FECHA</t>
   </si>
@@ -96,118 +96,85 @@
     <t>MERCANCIA_RECIBIDA</t>
   </si>
   <si>
-    <t>DIAS_FALTANTES_AL_RECIBIR</t>
-  </si>
-  <si>
     <t>STATUS</t>
   </si>
   <si>
+    <t>DIAS_RETRASO_AL_RECIBIR</t>
+  </si>
+  <si>
+    <t>FECHA_RECEPCION_REAL</t>
+  </si>
+  <si>
     <t>FO-SG-04-00</t>
   </si>
   <si>
-    <t>AVANTE20260924</t>
-  </si>
-  <si>
-    <t>mode09</t>
+    <t>AVANTE20261002</t>
+  </si>
+  <si>
+    <t>bacha07</t>
   </si>
   <si>
     <t>G03 - Gastos en general</t>
   </si>
   <si>
+    <t>MC. Jesús Alfredo Flores Osorio</t>
+  </si>
+  <si>
+    <t>PRUEBA</t>
+  </si>
+  <si>
+    <t>Contado</t>
+  </si>
+  <si>
+    <t>Transferencia Electrónica</t>
+  </si>
+  <si>
+    <t>PUE (pago en una sola exhibicion)</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>SI</t>
+  </si>
+  <si>
     <t>Luis Angel Lira</t>
   </si>
   <si>
-    <t>FINANCIERA</t>
-  </si>
-  <si>
-    <t>Contado</t>
-  </si>
-  <si>
-    <t>Transferencia Electrónica</t>
-  </si>
-  <si>
-    <t>PUE (pago en una sola exhibicion)</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>SI</t>
-  </si>
-  <si>
-    <t>María Luisa Martínez Morales</t>
-  </si>
-  <si>
-    <t>MC. Jesús Alfredo Flores Osorio</t>
-  </si>
-  <si>
     <t>MXN</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>$ 19,729.84</t>
-  </si>
-  <si>
-    <t>$ 3,156.77</t>
-  </si>
-  <si>
-    <t>$ 22,886.61</t>
+    <t>$ 11,332.00</t>
+  </si>
+  <si>
+    <t>$ 1,813.12</t>
+  </si>
+  <si>
+    <t>$ 13,145.12</t>
+  </si>
+  <si>
+    <t>PENDIENTE</t>
+  </si>
+  <si>
+    <t>PRUEBA HOJA</t>
+  </si>
+  <si>
+    <t>$ 21,024.15</t>
+  </si>
+  <si>
+    <t>$ 3,363.86</t>
+  </si>
+  <si>
+    <t>$ 24,388.01</t>
   </si>
   <si>
     <t>PARCIAL</t>
   </si>
   <si>
-    <t>$ 11,607.25</t>
-  </si>
-  <si>
-    <t>PENDIENTE DE MERCANCIA</t>
-  </si>
-  <si>
-    <t>PENDIENTE DE PAGO</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>herd05</t>
-  </si>
-  <si>
-    <t>PRUEBA ESTATUS</t>
-  </si>
-  <si>
-    <t>Crédito</t>
-  </si>
-  <si>
-    <t>Efectivo</t>
-  </si>
-  <si>
-    <t>$ 8,184.15</t>
-  </si>
-  <si>
-    <t>$ 1,309.46</t>
-  </si>
-  <si>
-    <t>$ 9,493.61</t>
-  </si>
-  <si>
-    <t>PENDIENTE</t>
-  </si>
-  <si>
-    <t>XXXX</t>
-  </si>
-  <si>
-    <t>FINALIZADO</t>
-  </si>
-  <si>
-    <t>-6</t>
-  </si>
-  <si>
-    <t>AVANTE 11,607.25</t>
-  </si>
-  <si>
-    <t>1</t>
+    <t>PENDIENTE PAGO Y MERCANCIA</t>
   </si>
 </sst>
 </file>
@@ -253,9 +220,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
@@ -593,7 +563,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45D375DD-15B7-4F53-9122-30FA48C9EA3E}">
-  <dimension ref="A1:Z4"/>
+  <dimension ref="A1:AA7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" bestFit="true" customWidth="true" width="9.44140625" collapsed="true"/>
@@ -619,7 +589,7 @@
     <col min="26" max="26" bestFit="true" customWidth="true" width="27.77734375" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>16</v>
       </c>
@@ -690,253 +660,190 @@
         <v>19</v>
       </c>
       <c r="X1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Y1" t="s">
         <v>22</v>
       </c>
       <c r="Z1" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1">
-        <v>46289.517945069441</v>
-      </c>
-      <c r="C2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D2" t="s">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="B2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+    </row>
+    <row r="3" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="B3" s="1"/>
+      <c r="L3" s="1"/>
+      <c r="M3" s="1"/>
+    </row>
+    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="B4" s="1"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="1"/>
+    </row>
+    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="B5" s="1"/>
+      <c r="L5" s="1"/>
+      <c r="M5" s="1"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="B6" t="n" s="2">
+        <v>46282.47662181713</v>
+      </c>
+      <c r="C6" t="s">
         <v>26</v>
       </c>
-      <c r="E2" t="s">
+      <c r="D6" t="s">
         <v>27</v>
       </c>
-      <c r="F2" t="s">
+      <c r="E6" t="s">
         <v>28</v>
       </c>
-      <c r="G2" t="s">
+      <c r="F6" t="s">
         <v>29</v>
       </c>
-      <c r="H2" t="s">
+      <c r="G6" t="s">
         <v>30</v>
       </c>
-      <c r="I2" t="s">
+      <c r="H6" t="s">
         <v>31</v>
       </c>
-      <c r="J2" t="s">
+      <c r="I6" t="s">
         <v>32</v>
       </c>
-      <c r="K2" t="s">
+      <c r="J6" t="s">
         <v>33</v>
       </c>
-      <c r="L2" s="1">
-        <v>46295.518404016206</v>
-      </c>
-      <c r="M2" s="1">
-        <v>46294.518495532408</v>
-      </c>
-      <c r="N2" t="s">
+      <c r="K6" t="s">
         <v>34</v>
       </c>
-      <c r="O2" t="s">
+      <c r="L6" t="n" s="3">
+        <v>46296.4774</v>
+      </c>
+      <c r="M6" t="n" s="4">
+        <v>46309.47866055556</v>
+      </c>
+      <c r="N6" t="s">
         <v>35</v>
       </c>
-      <c r="P2" t="s">
+      <c r="O6" t="s">
         <v>36</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="P6" t="s">
         <v>37</v>
       </c>
-      <c r="R2" t="s">
+      <c r="Q6" t="s">
+        <v>30</v>
+      </c>
+      <c r="R6" t="s">
         <v>38</v>
       </c>
-      <c r="S2" t="s">
+      <c r="S6" t="s">
         <v>39</v>
       </c>
-      <c r="T2" t="s">
+      <c r="T6" t="s">
         <v>40</v>
       </c>
-      <c r="U2" t="s">
+      <c r="U6" t="s">
         <v>41</v>
       </c>
-      <c r="V2" t="s">
+      <c r="V6" t="s">
         <v>42</v>
       </c>
-      <c r="W2" t="s">
-        <v>42</v>
-      </c>
-      <c r="X2" t="s">
-        <v>57</v>
-      </c>
-      <c r="Y2" t="s">
+      <c r="W6" t="s">
         <v>35</v>
       </c>
-      <c r="Z2" t="s">
+      <c r="X6" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="B7" t="n" s="5">
+        <v>46282.47662181713</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" t="s">
+        <v>27</v>
+      </c>
+      <c r="E7" t="s">
+        <v>28</v>
+      </c>
+      <c r="F7" t="s">
+        <v>29</v>
+      </c>
+      <c r="G7" t="s">
+        <v>30</v>
+      </c>
+      <c r="H7" t="s">
+        <v>31</v>
+      </c>
+      <c r="I7" t="s">
+        <v>32</v>
+      </c>
+      <c r="J7" t="s">
+        <v>33</v>
+      </c>
+      <c r="K7" t="s">
+        <v>34</v>
+      </c>
+      <c r="L7" t="n" s="6">
+        <v>46299.0</v>
+      </c>
+      <c r="M7" t="n" s="7">
+        <v>46309.0</v>
+      </c>
+      <c r="N7" t="s">
+        <v>35</v>
+      </c>
+      <c r="O7" t="s">
+        <v>36</v>
+      </c>
+      <c r="P7" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>30</v>
+      </c>
+      <c r="R7" t="s">
+        <v>38</v>
+      </c>
+      <c r="S7" t="s">
+        <v>39</v>
+      </c>
+      <c r="T7" t="s">
+        <v>45</v>
+      </c>
+      <c r="U7" t="s">
+        <v>46</v>
+      </c>
+      <c r="V7" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1">
-        <v>46289.517945069441</v>
-      </c>
-      <c r="C3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G3" t="s">
-        <v>29</v>
-      </c>
-      <c r="H3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I3" t="s">
-        <v>31</v>
-      </c>
-      <c r="J3" t="s">
-        <v>32</v>
-      </c>
-      <c r="K3" t="s">
-        <v>33</v>
-      </c>
-      <c r="L3" s="1">
-        <v>46295</v>
-      </c>
-      <c r="M3" s="1">
-        <v>46294</v>
-      </c>
-      <c r="N3" t="s">
-        <v>34</v>
-      </c>
-      <c r="O3" t="s">
+      <c r="W7" t="s">
         <v>35</v>
       </c>
-      <c r="P3" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>37</v>
-      </c>
-      <c r="R3" t="s">
-        <v>38</v>
-      </c>
-      <c r="S3" t="s">
-        <v>39</v>
-      </c>
-      <c r="T3" t="s">
-        <v>40</v>
-      </c>
-      <c r="U3" t="s">
-        <v>41</v>
-      </c>
-      <c r="V3" t="s">
-        <v>42</v>
-      </c>
-      <c r="W3" t="s">
-        <v>42</v>
-      </c>
-      <c r="X3" t="s">
-        <v>57</v>
-      </c>
-      <c r="Y3" t="s">
-        <v>35</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="B4" t="n" s="2">
-        <v>46282.58864228009</v>
-      </c>
-      <c r="C4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E4" t="s">
-        <v>48</v>
-      </c>
-      <c r="F4" t="s">
-        <v>28</v>
-      </c>
-      <c r="G4" t="s">
-        <v>37</v>
-      </c>
-      <c r="H4" t="s">
-        <v>49</v>
-      </c>
-      <c r="I4" t="s">
-        <v>50</v>
-      </c>
-      <c r="J4" t="s">
-        <v>51</v>
-      </c>
-      <c r="K4" t="s">
-        <v>33</v>
-      </c>
-      <c r="L4" t="n" s="3">
-        <v>46283.588922546296</v>
-      </c>
-      <c r="M4" t="n" s="4">
-        <v>46289.58924150463</v>
-      </c>
-      <c r="N4" t="s">
-        <v>34</v>
-      </c>
-      <c r="O4" t="s">
-        <v>35</v>
-      </c>
-      <c r="P4" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>36</v>
-      </c>
-      <c r="R4" t="s">
-        <v>38</v>
-      </c>
-      <c r="S4" t="s">
-        <v>39</v>
-      </c>
-      <c r="T4" t="s">
-        <v>52</v>
-      </c>
-      <c r="U4" t="s">
-        <v>53</v>
-      </c>
-      <c r="V4" t="s">
-        <v>54</v>
-      </c>
-      <c r="W4" t="s">
-        <v>54</v>
-      </c>
-      <c r="X4" t="s">
-        <v>57</v>
-      </c>
-      <c r="Y4" t="s">
-        <v>35</v>
-      </c>
-      <c r="Z4" t="s">
-        <v>58</v>
+      <c r="X7" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>44</v>
       </c>
     </row>
   </sheetData>
